--- a/Download/Allevamenti_ZP.xlsx
+++ b/Download/Allevamenti_ZP.xlsx
@@ -225,7 +225,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G5" t="n">
         <v>1.0</v>

--- a/Download/Allevamenti_ZP.xlsx
+++ b/Download/Allevamenti_ZP.xlsx
@@ -271,7 +271,7 @@
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G7" t="n">
         <v>4.0</v>
@@ -294,10 +294,10 @@
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="9">
@@ -317,10 +317,10 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0</v>
+        <v>19.0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="10">
@@ -340,10 +340,10 @@
         <v>18</v>
       </c>
       <c r="F10" t="n">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="G10" t="n">
-        <v>11.0</v>
+        <v>60.0</v>
       </c>
     </row>
     <row r="11">
@@ -363,10 +363,10 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="G11" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
     </row>
     <row r="12">
@@ -386,10 +386,10 @@
         <v>16</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/Allevamenti_ZP.xlsx
+++ b/Download/Allevamenti_ZP.xlsx
@@ -343,7 +343,7 @@
         <v>18.0</v>
       </c>
       <c r="G10" t="n">
-        <v>60.0</v>
+        <v>59.0</v>
       </c>
     </row>
     <row r="11">

--- a/Download/Allevamenti_ZP.xlsx
+++ b/Download/Allevamenti_ZP.xlsx
@@ -228,7 +228,7 @@
         <v>3.0</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
@@ -317,7 +317,7 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="G9" t="n">
         <v>13.0</v>
@@ -366,7 +366,7 @@
         <v>15.0</v>
       </c>
       <c r="G11" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="12">

--- a/Download/Allevamenti_ZP.xlsx
+++ b/Download/Allevamenti_ZP.xlsx
@@ -343,7 +343,7 @@
         <v>18.0</v>
       </c>
       <c r="G10" t="n">
-        <v>59.0</v>
+        <v>58.0</v>
       </c>
     </row>
     <row r="11">
